--- a/12610693.xlsx
+++ b/12610693.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,6 +240,30 @@
   </si>
   <si>
     <t>Vernika Mahajan</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>FELT LOW</t>
+  </si>
+  <si>
+    <t>felt stressed</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>felt good</t>
+  </si>
+  <si>
+    <t>felt high energy</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>feeling good</t>
   </si>
 </sst>
 </file>
@@ -1340,224 +1364,464 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>45</v>
+      </c>
+      <c r="D13" s="14">
+        <v>90</v>
+      </c>
+      <c r="E13" s="14">
+        <v>120</v>
+      </c>
+      <c r="F13" s="14">
+        <v>6</v>
+      </c>
+      <c r="G13" s="14">
+        <v>300</v>
+      </c>
+      <c r="H13" s="14">
+        <v>90</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>771</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>669</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B14" s="14">
+        <v>450</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>90</v>
+      </c>
+      <c r="F14" s="14">
+        <v>8</v>
+      </c>
+      <c r="G14" s="14">
+        <v>400</v>
+      </c>
+      <c r="H14" s="14">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>758</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>682</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>90</v>
+      </c>
+      <c r="E15" s="14">
+        <v>120</v>
+      </c>
+      <c r="F15" s="14">
+        <v>8</v>
+      </c>
+      <c r="G15" s="14">
+        <v>400</v>
+      </c>
+      <c r="H15" s="14">
+        <v>30</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>668</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>772</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B16" s="14">
+        <v>430</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
+        <v>250</v>
+      </c>
+      <c r="H16" s="14">
+        <v>30</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>705</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>240</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B18" s="14">
+        <v>510</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>200</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>90</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>45</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>90</v>
+      </c>
+      <c r="F19" s="14">
+        <v>2</v>
+      </c>
+      <c r="G19" s="14">
+        <v>100</v>
+      </c>
+      <c r="H19" s="14">
+        <v>30</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>707</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>733</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B20" s="14">
+        <v>400</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>90</v>
+      </c>
+      <c r="F20" s="14">
+        <v>8</v>
+      </c>
+      <c r="G20" s="14">
+        <v>400</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>708</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>732</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>45</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>5</v>
+      </c>
+      <c r="G21" s="14">
+        <v>250</v>
+      </c>
+      <c r="H21" s="14">
+        <v>30</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>45</v>
+      </c>
+      <c r="D22" s="14">
+        <v>240</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>945</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>495</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>
